--- a/artfynd/A 20789-2022 artfynd.xlsx
+++ b/artfynd/A 20789-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137515755</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137516987</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137515756</v>
       </c>
       <c r="B4" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137516986</v>
       </c>
       <c r="B5" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>137516985</v>
       </c>
       <c r="B6" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
